--- a/Kerim_Dane_ceny_mieszkan.xlsx
+++ b/Kerim_Dane_ceny_mieszkan.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0EC40F-9FED-4881-B758-B31C54D084D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4324C1CB-AE80-4DC0-89BC-EB71A45A19FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{336D2583-5C4C-4C42-9206-61D546232E49}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="82">
   <si>
     <t>Nazwa dewelopera</t>
   </si>
@@ -265,6 +265,18 @@
   </si>
   <si>
     <t>https://kerimdevelopment.pl/poznan-ul-bobrownicka-i/</t>
+  </si>
+  <si>
+    <t>Dereniowa</t>
+  </si>
+  <si>
+    <t>2026-09-24 00:00:00</t>
+  </si>
+  <si>
+    <t>Udział w działce drogowej</t>
+  </si>
+  <si>
+    <t>https://kerimdevelopment.pl/poznan-ul-dereniowa-ii/</t>
   </si>
 </sst>
 </file>
@@ -305,16 +317,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,9 +343,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -370,7 +383,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -476,7 +489,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -646,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA33353A-1A07-421F-B982-7CDBB172178E}">
-  <dimension ref="A1:BF4"/>
+  <dimension ref="A1:BF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -667,6 +680,7 @@
     <col min="28" max="28" width="9.44140625" customWidth="1"/>
     <col min="29" max="29" width="15.21875" customWidth="1"/>
     <col min="30" max="30" width="11.6640625" customWidth="1"/>
+    <col min="33" max="33" width="19.77734375" customWidth="1"/>
     <col min="34" max="34" width="11.5546875" customWidth="1"/>
     <col min="36" max="36" width="15.77734375" customWidth="1"/>
     <col min="37" max="37" width="15.6640625" customWidth="1"/>
@@ -1220,51 +1234,356 @@
       </c>
     </row>
     <row r="4" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
-      <c r="AG4" s="4"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="4"/>
-      <c r="AR4" s="4"/>
-      <c r="AS4" s="4"/>
-      <c r="AU4" s="4"/>
-      <c r="AV4" s="4"/>
-      <c r="AW4" s="4"/>
-      <c r="AX4" s="4"/>
-      <c r="AY4" s="4"/>
-      <c r="AZ4" s="4"/>
-      <c r="BA4" s="1"/>
-      <c r="BB4" s="3"/>
-      <c r="BC4" s="4"/>
-      <c r="BD4" s="4"/>
-      <c r="BE4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1">
+        <v>5252970002</v>
+      </c>
+      <c r="F4" s="1">
+        <v>52619039300000</v>
+      </c>
+      <c r="G4" s="1">
+        <v>502450566</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <v>9885.67</v>
+      </c>
+      <c r="AM4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN4">
+        <v>1885000</v>
+      </c>
+      <c r="AO4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP4">
+        <v>1890000</v>
+      </c>
+      <c r="AQ4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT4">
+        <v>5000</v>
+      </c>
+      <c r="AU4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AW4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AX4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AY4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AZ4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="BB4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="BC4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="BF4" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1">
+        <v>5252970002</v>
+      </c>
+      <c r="F5" s="1">
+        <v>52619039300000</v>
+      </c>
+      <c r="G5" s="1">
+        <v>502450566</v>
+      </c>
+      <c r="H5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK5">
+        <v>2</v>
+      </c>
+      <c r="AL5">
+        <v>9885.67</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN5">
+        <v>1885000</v>
+      </c>
+      <c r="AO5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP5">
+        <v>1890000</v>
+      </c>
+      <c r="AQ5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT5">
+        <v>5000</v>
+      </c>
+      <c r="AU5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AW5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AX5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AY5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AZ5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="BB5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="BC5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="BF5" s="6" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
